--- a/.claude/docs/Example橋脚4/export/0622_直角方向基礎.xlsx
+++ b/.claude/docs/Example橋脚4/export/0622_直角方向基礎.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="206">
   <si>
-    <t>9.11 基礎の照査</t>
+    <t>9.10 基礎の照査</t>
   </si>
   <si>
     <t>作用の組合せで求めた応答値に応答値係数γRを乗じたものを設計応答値とする．地盤および</t>
